--- a/forms/trg/Formulir_TRG_ggerg.xlsx
+++ b/forms/trg/Formulir_TRG_ggerg.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!B5:B31)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,12 +925,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Akbar Walenna, Ph.D.</t>
+          <t>Prof. Dr. Eng. Tri Harianto</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Achmad Bakri Muhiddin, Ph.D.</t>
+          <t>Muhammad Akbar Walenna, Ph.D.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Farid Sitepu, MT.</t>
+          <t>Prof. Achmad Bakri Muhiddin, Ph.D.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>St. Hiraini Nur, MT.</t>
+          <t>Farid Sitepu, MT.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Ariningsih Suprapti, MT.</t>
+          <t>St. Hiraini Nur, MT.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Andi Muhamad Pramatadie, S.T., M.Eng., Ph.D</t>
+          <t>Ariningsih Suprapti, MT.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1099,24 +1099,16 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Marolo C. Alfaro, P.Eng.</t>
+          <t>Andi Muhamad Pramatadie, S.T., M.Eng., Ph.D</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>University of manitoba (canada)</t>
-        </is>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>xx</t>
-        </is>
-      </c>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1136,17 +1128,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Dr. Alsidqi Hasan</t>
+          <t>Prof. Dr. Marolo C. Alfaro, P.Eng.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universiti Malaysia Sarawak (MALAYSIA)</t>
+          <t>University of manitoba (canada)</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1173,17 +1165,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Takenori Hino</t>
+          <t>Assoc. Prof. Dr. Alsidqi Hasan</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Saga University (Japan)</t>
+          <t>Universiti Malaysia Sarawak (MALAYSIA)</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1210,17 +1202,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dr. Zijun Wang</t>
+          <t>Prof. Dr. Takenori Hino</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Beijing Jiaotong University (China)</t>
+          <t>Saga University (Japan)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1247,17 +1239,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Esdras Ngezahayo, Ph.D.</t>
+          <t>Dr. Zijun Wang</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>University of Birmingham (United Kingdom)</t>
+          <t>Beijing Jiaotong University (China)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1284,16 +1276,24 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Hairulla</t>
+          <t>Esdras Ngezahayo, Ph.D.</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>University of Birmingham (United Kingdom)</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Andi Hutami Endang</t>
+          <t>Hairulla</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1342,20 +1342,16 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Dian Pratiwi Aggeraini</t>
+          <t>Andi Hutami Endang</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>GGERG Team</t>
-        </is>
-      </c>
+      <c r="E18" s="11" t="n"/>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1373,10 +1369,22 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Dian Pratiwi Aggeraini</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>GGERG Team</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1384,7 +1392,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1573,15 +1585,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
